--- a/config/excel/CfgRoomLayouts.xlsx
+++ b/config/excel/CfgRoomLayouts.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoomLayouts" sheetId="1" r:id="R4b75710186f0464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoomLayouts" sheetId="1" r:id="R531235c6712c40f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,6 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.###"/>
+    <x:numFmt numFmtId="202" formatCode="General"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -29,7 +34,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -44,6 +49,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -58,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -80,6 +115,39 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -287,218 +355,518 @@
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.5" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23.100000381469727" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="25.299999237060547" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26.25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28.75" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="17.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>HalfExtent</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>WallHeight</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>WallThickness</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>ExitHalfWidth</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>SpawnInset</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="16" t="str">
         <x:v>ExitCenterInset</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="16" t="str">
         <x:v>ExitInteractionRadius</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="16" t="str">
         <x:v>ObjectInteractionRadius</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="16" t="str">
         <x:v>ChestX</x:v>
       </x:c>
-      <x:c r="K1" s="5" t="str">
+      <x:c r="K1" s="16" t="str">
         <x:v>ChestZ</x:v>
       </x:c>
-      <x:c r="L1" s="5" t="str">
+      <x:c r="L1" s="16" t="str">
         <x:v>NpcX</x:v>
       </x:c>
-      <x:c r="M1" s="5" t="str">
+      <x:c r="M1" s="16" t="str">
         <x:v>NpcZ</x:v>
       </x:c>
-      <x:c r="N1" s="5" t="str">
+      <x:c r="N1" s="16" t="str">
         <x:v>ExtractionX</x:v>
       </x:c>
-      <x:c r="O1" s="5" t="str">
+      <x:c r="O1" s="16" t="str">
         <x:v>ExtractionZ</x:v>
       </x:c>
-      <x:c r="P1" s="5" t="str">
+      <x:c r="P1" s="16" t="str">
         <x:v>ObstacleHeight</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="17" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="K2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="L2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="M2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="N2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="O2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="P2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+      <x:c r="B2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="C2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="D2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="F2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="G2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="H2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="I2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="J2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="K2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="L2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="M2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="N2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="O2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="P2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="18" t="str">
         <x:v># 布局编号</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="18" t="str">
         <x:v>房间半边长</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="18" t="str">
         <x:v>边界墙高度</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="18" t="str">
         <x:v>边界墙厚度</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str">
+      <x:c r="E3" s="18" t="str">
         <x:v>出口半宽</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str">
+      <x:c r="F3" s="18" t="str">
         <x:v>入场点距边界内缩</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="str">
+      <x:c r="G3" s="18" t="str">
         <x:v>出口标志距边界内缩</x:v>
       </x:c>
-      <x:c r="H3" s="8" t="str">
+      <x:c r="H3" s="18" t="str">
         <x:v>出口交互半径</x:v>
       </x:c>
-      <x:c r="I3" s="8" t="str">
+      <x:c r="I3" s="18" t="str">
         <x:v>物件交互半径</x:v>
       </x:c>
-      <x:c r="J3" s="8" t="str">
+      <x:c r="J3" s="18" t="str">
         <x:v>箱子局部X</x:v>
       </x:c>
-      <x:c r="K3" s="8" t="str">
+      <x:c r="K3" s="18" t="str">
         <x:v>箱子局部Z</x:v>
       </x:c>
-      <x:c r="L3" s="8" t="str">
+      <x:c r="L3" s="18" t="str">
         <x:v>NPC局部X</x:v>
       </x:c>
-      <x:c r="M3" s="8" t="str">
+      <x:c r="M3" s="18" t="str">
         <x:v>NPC局部Z</x:v>
       </x:c>
-      <x:c r="N3" s="8" t="str">
+      <x:c r="N3" s="18" t="str">
         <x:v>撤离点局部X</x:v>
       </x:c>
-      <x:c r="O3" s="8" t="str">
+      <x:c r="O3" s="18" t="str">
         <x:v>撤离点局部Z</x:v>
       </x:c>
-      <x:c r="P3" s="8" t="str">
+      <x:c r="P3" s="18" t="str">
         <x:v>障碍显示高度</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="n">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="19" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="n">
+      <x:c r="C4" s="19" t="n">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="n">
+      <x:c r="D4" s="19" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="n">
+      <x:c r="E4" s="19" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G4" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="3" t="n">
+      <x:c r="F4" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G4" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="19" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="I4" s="3" t="n">
+      <x:c r="I4" s="19" t="n">
         <x:v>2.2</x:v>
       </x:c>
-      <x:c r="J4" s="3" t="n">
+      <x:c r="J4" s="19" t="n">
         <x:v>-4</x:v>
       </x:c>
-      <x:c r="K4" s="3" t="n">
+      <x:c r="K4" s="19" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="L4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="3" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="O4" s="3" t="n">
+      <x:c r="L4" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N4" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O4" s="19" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="P4" s="3" t="n">
+      <x:c r="P4" s="19" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C5" s="19" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D5" s="19" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F5" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G5" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="19" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I5" s="19" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J5" s="19" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="K5" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L5" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O5" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="P5" s="19" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="19" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G6" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="19" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I6" s="19" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J6" s="19" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="K6" s="19" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="L6" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O6" s="19" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="P6" s="19" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="19" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D7" s="19" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G7" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="19" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I7" s="19" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J7" s="19" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L7" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O7" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="P7" s="19" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="19" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I8" s="19" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="K8" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L8" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O8" s="19" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="P8" s="19" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="19" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I9" s="19" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="K9" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L9" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O9" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P9" s="19" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C10" s="19" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E10" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F10" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G10" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="19" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I10" s="19" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J10" s="19" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O10" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="19" t="n">
         <x:v>1.6</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgRoomLayouts.xlsx
+++ b/config/excel/CfgRoomLayouts.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoomLayouts" sheetId="1" r:id="R531235c6712c40f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoomLayouts" sheetId="1" r:id="R6f1a0d28883f4d77"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,6 +870,106 @@
         <x:v>1.6</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="K11" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O11" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="P11" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J12" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="K12" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O12" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="P12" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
